--- a/real_world_test/selected_real_world_projects.xlsx
+++ b/real_world_test/selected_real_world_projects.xlsx
@@ -516,25 +516,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>unclebob/fitnesse</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/unclebob/fitnesse/commit/ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2755,46 +2755,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>vaadin/framework</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>47</v>
+        <v>360</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>checker/jtreg/nullness/PersistUtil.java:writeTestFile</t>
+          <t>server/src/main/java/com/vaadin/server/BootstrapHandler.java:writeBootstrapPage</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>checker/jtreg/nullness/PersistUtil.java:@@ -40,9 +40,9 @@</t>
+          <t>server/src/main/java/com/vaadin/server/BootstrapHandler.java@@ -353,10 +353,10 @@</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>java.io.PrintWriter</t>
+          <t>java.io.BufferedWriter,java.io.OutputStreamWriter</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>writer</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>checker/jtreg/nullness/PersistUtil.java:43</t>
+          <t>server/src/main/java/com/vaadin/server/BootstrapHandler.java:356</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2844,53 +2844,53 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>1011</v>
+        <v>1035</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>vaadin/framework</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>dataflow/src/main/java/org/checkerframework/dataflow/cfg/visualize/DOTCFGVisualizer.java:visualize</t>
+          <t>server/src/main/java/com/vaadin/server/UnsupportedBrowserHandler.java:writeBrowserTooOldPage</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>dataflow/src/main/java/org/checkerframework/dataflow/cfg/visualize/DOTCFGVisualizer.java@@ -84,11 +84,8 @@</t>
+          <t>server/src/main/java/com/vaadin/server/UnsupportedBrowserHandler.java@@ -61,34 +61,33 @@</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>java.io.BufferedWriter</t>
+          <t>java.io.Writer</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>page</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>dataflow/src/main/java/org/checkerframework/dataflow/cfg/visualize/DOTCFGVisualizer.java:89</t>
+          <t>server/src/main/java/com/vaadin/server/UnsupportedBrowserHandler.java:64</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2940,53 +2940,53 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>vaadin/framework</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>862</v>
+        <v>1506</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/common/wholeprograminference/WholeProgramInferenceJavaParserStorage.java:writeAjavaFile</t>
+          <t>server/src/main/java/com/vaadin/server/VaadinService.java:writeStringResponse</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/common/wholeprograminference/WholeProgramInferenceJavaParserStorage.java@@ -808,8 +809,7 @@</t>
+          <t>server/src/main/java/com/vaadin/server/VaadinService.java@@ -1499,10 +1499,10 @@</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>java.io.FileWriter</t>
+          <t>java.io.PrintWriter,java.io.BufferedWriter,java.io.OutputStreamWriter</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>writer</t>
+          <t>outWriter</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/common/wholeprograminference/WholeProgramInferenceJavaParserStorage.java:812</t>
+          <t>server/src/main/java/com/vaadin/server/VaadinService.java:1502</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3036,53 +3036,53 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>1013</v>
+        <v>1038</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>vaadin/framework</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>532</v>
+        <v>685</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/ajava/InsertAjavaAnnotations.java:insertAnnotations</t>
+          <t>server/src/main/java/com/vaadin/server/communication/FileUploadHandler.java:sendUploadResponse</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/ajava/InsertAjavaAnnotations.java@@ -517,10 +517,10 @@</t>
+          <t>server/src/main/java/com/vaadin/server/communication/FileUploadHandler.java@@ -676,12 +676,12 @@</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>java.io.FileInputStream</t>
+          <t>java.io.OutputStream</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>annotationInputStream</t>
+          <t>out</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/ajava/InsertAjavaAnnotations.java:520</t>
+          <t>server/src/main/java/com/vaadin/server/communication/FileUploadHandler.java:679</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3132,53 +3132,53 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>1014</v>
+        <v>1039</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>vaadin/framework</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/stub/RemoveAnnotationsForInference.java:removeAnnotations</t>
+          <t>server/src/main/java/com/vaadin/server/communication/PortletDummyRequestHandler.java:handleRequest</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/stub/RemoveAnnotationsForInference.java@@ -199,12 +201,11 @@</t>
+          <t>server/src/main/java/com/vaadin/server/communication/PortletDummyRequestHandler.java@@ -60,10 +60,10 @@</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>pw</t>
+          <t>outWriter</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/stub/RemoveAnnotationsForInference.java:203</t>
+          <t>server/src/main/java/com/vaadin/server/communication/PortletDummyRequestHandler.java:63</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3228,53 +3228,53 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>1015</v>
+        <v>1040</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>vaadin/framework</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>622</v>
+        <v>106</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/util/CheckerMain.java:outputArgumentsToFile</t>
+          <t>server/src/main/java/com/vaadin/server/communication/ResourceWriter.java:write</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/util/CheckerMain.java@@ -576,11 +576,10 @@</t>
+          <t>server/src/main/java/com/vaadin/server/communication/ResourceWriter.java@@ -82,15 +83,13 @@</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>java.io.PrintWriter</t>
+          <t>java.io.InputStreamReader</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>writer</t>
+          <t>r</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>framework/src/main/java/org/checkerframework/framework/util/CheckerMain.java:580</t>
+          <t>server/src/main/java/com/vaadin/server/communication/ResourceWriter.java:86</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3324,53 +3324,53 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>1016</v>
+        <v>1041</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>typetools/checker-framework</t>
+          <t>vaadin/framework</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/typetools/checker-framework/commit/b2081204740a919a5d4d7babca8cdd9480c74d56</t>
+          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>javacutil/src/main/java/org/checkerframework/javacutil/SystemUtil.java:readFile</t>
+          <t>server/src/main/java/com/vaadin/server/widgetsetutils/WidgetSetBuilder.java:updateWidgetSet</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>javacutil/src/main/java/org/checkerframework/javacutil/SystemUtil.java@@ -196,15 +196,14 @@</t>
+          <t>server/src/main/java/com/vaadin/server/widgetsetutils/WidgetSetBuilder.java@@ -84,12 +84,12 @@</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>java.io.BufferedReader</t>
+          <t>java.io.PrintStream,java.io.FileOutputStream</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>br</t>
+          <t>printStream</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>javacutil/src/main/java/org/checkerframework/javacutil/SystemUtil.java</t>
+          <t>server/src/main/java/com/vaadin/server/widgetsetutils/WidgetSetBuilder.java:87</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3420,53 +3420,53 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>235d29e2ece809f5fdda41a7c5ab6a8ffef02fd6</t>
+          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1034</v>
+        <v>948</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>vaadin/framework</t>
+          <t>stanfordnlp/CoreNLP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/BootstrapHandler.java:writeBootstrapPage</t>
+          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:initializeAndRunCoref</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/BootstrapHandler.java@@ -353,10 +353,10 @@</t>
+          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java@@ -366,9 +366,9 @@</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>java.io.BufferedWriter,java.io.OutputStreamWriter</t>
+          <t>java.io.FileInputStream</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>writer</t>
+          <t>fis</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/BootstrapHandler.java:356</t>
+          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:369</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -3516,53 +3516,53 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1035</v>
+        <v>949</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>vaadin/framework</t>
+          <t>stanfordnlp/CoreNLP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>93</v>
+        <v>290</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/UnsupportedBrowserHandler.java:writeBrowserTooOldPage</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java:readObjectFromFile</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/UnsupportedBrowserHandler.java@@ -61,34 +61,33 @@</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java@@ -273,19 +273,17 @@</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>java.io.Writer</t>
+          <t>java.io.ObjectInputStream,java.io.BufferedInputStream,java.util.zip.GZIPInputStream</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>ois,ois</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/UnsupportedBrowserHandler.java:64</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java:278,284</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3612,53 +3612,53 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1036</v>
+        <v>950</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>vaadin/framework</t>
+          <t>stanfordnlp/CoreNLP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1506</v>
+        <v>314</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/VaadinService.java:writeStringResponse</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java:readObjectFromURLOrClasspathOrFileSystem</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/VaadinService.java@@ -1499,10 +1499,10 @@</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java@@ -307,10 +305,10 @@</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>java.io.PrintWriter,java.io.BufferedWriter,java.io.OutputStreamWriter</t>
+          <t>java.io.ObjectInputStream</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>outWriter</t>
+          <t>ois</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/VaadinService.java:1502</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java:310</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3708,53 +3708,53 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1038</v>
+        <v>951</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>vaadin/framework</t>
+          <t>stanfordnlp/CoreNLP</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>685</v>
+        <v>1224</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/FileUploadHandler.java:sendUploadResponse</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java:slurpURL</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/FileUploadHandler.java@@ -676,12 +676,12 @@</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java@@ -1213,14 +1211,14 @@</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>java.io.OutputStream</t>
+          <t>java.io.BufferedReader,java.io.InputStreamReader</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>br</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/FileUploadHandler.java:679</t>
+          <t>src/edu/stanford/nlp/io/IOUtils.java:1216</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3804,53 +3804,51 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1039</v>
+        <v>952</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>vaadin/framework</t>
+          <t>stanfordnlp/CoreNLP</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>318</v>
       </c>
       <c r="H34" t="n">
-        <v>69</v>
+        <v>397</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/PortletDummyRequestHandler.java:handleRequest</t>
+          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:initializeAndRunCoref</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/PortletDummyRequestHandler.java@@ -60,10 +60,10 @@</t>
+          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java@@ -366,9 +366,9 @@</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3875,7 +3873,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>java.io.PrintWriter</t>
+          <t xml:space="preserve">java.io.FileInputStream </t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3885,12 +3883,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>outWriter</t>
+          <t>fis</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/PortletDummyRequestHandler.java:63</t>
+          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:369</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -3900,53 +3898,53 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1040</v>
+        <v>1021</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>vaadin/framework</t>
+          <t>unclebob/fitnesse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>https://github.com/unclebob/fitnesse/commit/ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/ResourceWriter.java:write</t>
+          <t>src/fit/FileRunner.java:read</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/ResourceWriter.java@@ -82,15 +83,13 @@</t>
+          <t>src/fit/FileRunner.java@@ -63,8 +63,11 @@</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3961,7 +3959,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>try-with</t>
+          <t>CloseInFinally</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3971,7 +3969,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>java.io.InputStreamReader</t>
+          <t>java.io.FileReader</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3981,12 +3979,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>in</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/communication/ResourceWriter.java:86</t>
+          <t>src/fit/FileRunner.java:65</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -3996,53 +3994,53 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1041</v>
+        <v>1022</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>vaadin/framework</t>
+          <t>unclebob/fitnesse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://github.com/vaadin/framework/commit/6b8f9779fbc8c81d1dff2ac139bd41535018aa78</t>
+          <t>https://github.com/unclebob/fitnesse/commit/ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/widgetsetutils/WidgetSetBuilder.java:updateWidgetSet</t>
+          <t>src/fitnesse/ConfigurationParameter.java:loadProperties</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/widgetsetutils/WidgetSetBuilder.java@@ -84,12 +84,12 @@</t>
+          <t>src/fitnesse/ConfigurationParameter.java@@ -81,9 +81,14 @@</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4057,7 +4055,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>try-with</t>
+          <t>CloseInFinally</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4067,7 +4065,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>java.io.PrintStream,java.io.FileOutputStream</t>
+          <t>java.io.FileInputStream</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4077,12 +4075,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>printStream</t>
+          <t>propertiesStream</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>server/src/main/java/com/vaadin/server/widgetsetutils/WidgetSetBuilder.java:87</t>
+          <t>src/fitnesse/ConfigurationParameter.java:72</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4092,53 +4090,53 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>53701564b197d1d30bd3dbc2f4e6a8d01b01b25a</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
+          <t>ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>948</v>
+        <v>1023</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stanfordnlp/CoreNLP</t>
+          <t>unclebob/fitnesse</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
+          <t>https://github.com/unclebob/fitnesse/commit/ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>397</v>
+        <v>50</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:initializeAndRunCoref</t>
+          <t>src/fitnesse/junit/JavaFormatter.java:copy</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java@@ -366,9 +366,9 @@</t>
+          <t>src/fitnesse/junit/JavaFormatter.java@@ -37,16 +37,21 @@</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4153,7 +4151,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>try-with</t>
+          <t>CloseInFinally</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4163,7 +4161,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>java.io.FileInputStream</t>
+          <t>java.io.InputStream,java.io.OutputStream</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4173,12 +4171,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>in,out</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:369</t>
+          <t>src/fitnesse/junit/JavaFormatter.java:40,41</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4188,53 +4186,53 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
+          <t>ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>949</v>
+        <v>1024</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stanfordnlp/CoreNLP</t>
+          <t>unclebob/fitnesse</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
+          <t>https://github.com/unclebob/fitnesse/commit/ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>290</v>
+        <v>185</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java:readObjectFromFile</t>
+          <t>src/fitnesse/wiki/fs/ZipFileVersionsController.java:addToZip</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java@@ -273,19 +273,17 @@</t>
+          <t>src/fitnesse/wiki/fs/ZipFileVersionsController.java@@ -175,13 +175,16 @@</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4249,7 +4247,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>try-with</t>
+          <t>CloseInFinally</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4259,7 +4257,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>java.io.ObjectInputStream,java.io.BufferedInputStream,java.util.zip.GZIPInputStream</t>
+          <t>java.io.FileInputStream</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4269,12 +4267,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>ois,ois</t>
+          <t>is</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java:278,284</t>
+          <t>src/fitnesse/wiki/fs/ZipFileVersionsController.java:173</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -4284,53 +4282,53 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
+          <t>ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>950</v>
+        <v>1025</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stanfordnlp/CoreNLP</t>
+          <t>unclebob/fitnesse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
+          <t>https://github.com/unclebob/fitnesse/commit/ffd57b67b4703d1672480d5251f307def18f628f</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java:readObjectFromURLOrClasspathOrFileSystem</t>
+          <t>src/util/FileUtil.java:getFileLines</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java@@ -307,10 +305,10 @@</t>
+          <t>src/util/FileUtil.java@@ -142,10 +142,12 @@</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4345,7 +4343,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>try-with</t>
+          <t>CloseInFinally</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4355,7 +4353,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>java.io.ObjectInputStream</t>
+          <t>java.io.BufferedReader</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4365,12 +4363,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>ois</t>
+          <t>reader</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java:310</t>
+          <t>src/util/FileUtil.java:143</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -4380,197 +4378,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>951</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>stanfordnlp/CoreNLP</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>1224</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java:slurpURL</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java@@ -1213,14 +1211,14 @@</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>noCloseEPath</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>try-with</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>java.io.BufferedReader,java.io.InputStreamReader</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>br</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>src/edu/stanford/nlp/io/IOUtils.java:1216</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>local variable</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>0a061469ec491ae4512d98233ca15e76caafe20b</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>952</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>stanfordnlp/CoreNLP</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://github.com/stanfordnlp/CoreNLP/commit/0a061469ec491ae4512d98233ca15e76caafe20b</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>318</v>
-      </c>
-      <c r="H41" t="n">
-        <v>397</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:initializeAndRunCoref</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java@@ -366,9 +366,9 @@</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>noCloseEPath</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>try-with</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">java.io.FileInputStream </t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>fis</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>src/edu/stanford/nlp/dcoref/SieveCoreferenceSystem.java:369</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>local variable</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>28a10fca03e8f6c0f6aaaa39fc7817d574fb014b</t>
+          <t>2b8cce7c23b8804b71ed41c418a7a056f7feb780</t>
         </is>
       </c>
     </row>
